--- a/Manufacturing Form July 2026 to Mohamad.xlsx
+++ b/Manufacturing Form July 2026 to Mohamad.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Nagi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Odoo 19\server\odoo\addons\maz_alumec_ajo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80B88144-CBC7-4363-B732-8C9FCA8E6CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{356BEEB7-0B4B-44BA-8D7B-E09849DFB3B0}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="25815" windowHeight="14025"/>
   </bookViews>
   <sheets>
     <sheet name="1 LSHW- FXI-F1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'1 LSHW- FXI-F1'!$A$1:$P$271</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -320,7 +319,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -742,9 +741,9 @@
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{448F0135-7071-48D6-9F23-5134EBA7AD04}"/>
-    <cellStyle name="Normal_EXECOB" xfId="2" xr:uid="{53E45898-5FB5-4CE8-9642-8457EDEFDA27}"/>
-    <cellStyle name="Normal_HINGED" xfId="3" xr:uid="{AA32186B-75CD-47C7-8C4C-8E6FC9B0C32F}"/>
+    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal_EXECOB" xfId="2"/>
+    <cellStyle name="Normal_HINGED" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -779,7 +778,7 @@
         <xdr:cNvPr id="2" name="Rectangle 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0076BCE5-2F02-48B0-A6CB-6D54A4CAC056}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0076BCE5-2F02-48B0-A6CB-6D54A4CAC056}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -837,7 +836,7 @@
         <xdr:cNvPr id="3" name="Straight Connector 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA1F763D-4EE6-4A38-AFE4-110B14542378}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EA1F763D-4EE6-4A38-AFE4-110B14542378}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -889,7 +888,7 @@
         <xdr:cNvPr id="4" name="Straight Connector 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A4AA073-9E37-4763-8209-516E524DCA79}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{1A4AA073-9E37-4763-8209-516E524DCA79}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -936,7 +935,7 @@
         <xdr:cNvPr id="5" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06E2C471-967C-4EEE-83DE-CB87E3A7F663}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{06E2C471-967C-4EEE-83DE-CB87E3A7F663}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -977,13 +976,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>29</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -993,7 +992,7 @@
                   <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{304573E7-333D-4029-84DB-B44FE3FB5BCD}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{304573E7-333D-4029-84DB-B44FE3FB5BCD}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1045,7 +1044,7 @@
         <xdr:cNvPr id="6" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFBCB29-96F4-452F-97E5-2079F3C0A577}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{EAFBCB29-96F4-452F-97E5-2079F3C0A577}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1092,7 +1091,7 @@
         <xdr:cNvPr id="7" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AF3E6DD8-5DE6-43F9-99DA-A9F777EFA5A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AF3E6DD8-5DE6-43F9-99DA-A9F777EFA5A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1139,7 +1138,7 @@
         <xdr:cNvPr id="8" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DFD79E94-F208-4216-A2D3-97C2D0A0A550}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{DFD79E94-F208-4216-A2D3-97C2D0A0A550}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1186,7 +1185,7 @@
         <xdr:cNvPr id="9" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34552D17-8607-4FD2-BDC1-83A4729135A1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{34552D17-8607-4FD2-BDC1-83A4729135A1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1233,7 +1232,7 @@
         <xdr:cNvPr id="10" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CA4DDE3-3A91-4F43-B3D4-720D9B107608}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6CA4DDE3-3A91-4F43-B3D4-720D9B107608}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1280,7 +1279,7 @@
         <xdr:cNvPr id="11" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B65DF84C-AEF5-4E8D-AED9-97DC8F2AD86E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B65DF84C-AEF5-4E8D-AED9-97DC8F2AD86E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1327,7 +1326,7 @@
         <xdr:cNvPr id="12" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F609C720-3415-49AB-8B69-115BED20A4C5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F609C720-3415-49AB-8B69-115BED20A4C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1374,7 +1373,7 @@
         <xdr:cNvPr id="13" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6D5273B-1878-4F1B-BCB7-077752B6D7BD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E6D5273B-1878-4F1B-BCB7-077752B6D7BD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1421,7 +1420,7 @@
         <xdr:cNvPr id="14" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01B2CE24-DD2E-456C-ABB8-8198011E0685}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{01B2CE24-DD2E-456C-ABB8-8198011E0685}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1462,13 +1461,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>25</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1478,7 +1477,7 @@
                   <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17ACAAD5-4279-4AB8-8068-9C37183C07B9}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{17ACAAD5-4279-4AB8-8068-9C37183C07B9}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1524,13 +1523,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1540,7 +1539,7 @@
                   <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DC62CEE-F558-4B93-85FF-EB678BD0F430}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{4DC62CEE-F558-4B93-85FF-EB678BD0F430}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1597,7 +1596,7 @@
         <xdr:cNvPr id="15" name="Rectangle 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3540D93B-CD37-4BE2-8428-A5FF94F57157}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{3540D93B-CD37-4BE2-8428-A5FF94F57157}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1655,7 +1654,7 @@
         <xdr:cNvPr id="16" name="Straight Connector 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63D2F311-4C19-44E0-882C-43AF39899CBE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63D2F311-4C19-44E0-882C-43AF39899CBE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1707,7 +1706,7 @@
         <xdr:cNvPr id="17" name="Straight Connector 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9EABD69D-3BA6-47B4-B269-428F441D582A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{9EABD69D-3BA6-47B4-B269-428F441D582A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1754,7 +1753,7 @@
         <xdr:cNvPr id="18" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEEDE03C-B590-4ECE-8632-3CB7C5FC6A00}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{BEEDE03C-B590-4ECE-8632-3CB7C5FC6A00}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1795,13 +1794,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>97</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>97</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1811,7 +1810,7 @@
                   <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A4E914B-F268-405D-8E10-818EDD129710}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6A4E914B-F268-405D-8E10-818EDD129710}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1863,7 +1862,7 @@
         <xdr:cNvPr id="19" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A997CF7A-3BCB-48A5-B937-B5FBBA3B054A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A997CF7A-3BCB-48A5-B937-B5FBBA3B054A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1910,7 +1909,7 @@
         <xdr:cNvPr id="20" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{38893813-3C7A-4F6F-9BCF-6EB80BF3E896}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{38893813-3C7A-4F6F-9BCF-6EB80BF3E896}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1957,7 +1956,7 @@
         <xdr:cNvPr id="21" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AABC6CC3-CD86-49CE-9691-54FEFD7F2DE0}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AABC6CC3-CD86-49CE-9691-54FEFD7F2DE0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2004,7 +2003,7 @@
         <xdr:cNvPr id="22" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2C230C8-BC47-44B6-B100-DDE2321D5140}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2C230C8-BC47-44B6-B100-DDE2321D5140}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2051,7 +2050,7 @@
         <xdr:cNvPr id="23" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F21DB7E7-5BD4-4DA8-9BAF-7EF8E5511B41}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F21DB7E7-5BD4-4DA8-9BAF-7EF8E5511B41}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2098,7 +2097,7 @@
         <xdr:cNvPr id="24" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4056AB8-AA26-4468-8AE8-6682267C0DCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C4056AB8-AA26-4468-8AE8-6682267C0DCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2139,13 +2138,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>93</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>93</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2155,7 +2154,7 @@
                   <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E88EFAC0-CEC0-46D0-9FDC-2EF737F1E86E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E88EFAC0-CEC0-46D0-9FDC-2EF737F1E86E}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2201,13 +2200,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>94</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>94</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2217,7 +2216,7 @@
                   <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C40D0DCD-47C4-4D36-BB81-79DCEBE247E8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C40D0DCD-47C4-4D36-BB81-79DCEBE247E8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2269,7 +2268,7 @@
         <xdr:cNvPr id="25" name="Picture 24" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F63FD9B4-CF04-4EA7-B3C4-6AAC142C7900}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F63FD9B4-CF04-4EA7-B3C4-6AAC142C7900}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2320,7 +2319,7 @@
         <xdr:cNvPr id="26" name="Picture 25" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63A7E243-366D-4744-8113-5656EB403BCB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{63A7E243-366D-4744-8113-5656EB403BCB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2376,7 +2375,7 @@
         <xdr:cNvPr id="27" name="Rectangle 26">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2328E3E-AC00-470A-A255-B65AFF026AC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{C2328E3E-AC00-470A-A255-B65AFF026AC4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2434,7 +2433,7 @@
         <xdr:cNvPr id="28" name="Straight Connector 27">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F4978A9-5409-4378-B917-21B386A9B18C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6F4978A9-5409-4378-B917-21B386A9B18C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2486,7 +2485,7 @@
         <xdr:cNvPr id="29" name="Straight Connector 28">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F16F9E74-0E02-4445-A301-9A7DABB3AC50}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{F16F9E74-0E02-4445-A301-9A7DABB3AC50}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2533,7 +2532,7 @@
         <xdr:cNvPr id="30" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7C5725D-70D5-4DC6-A939-9430B4B22B0C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E7C5725D-70D5-4DC6-A939-9430B4B22B0C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2574,13 +2573,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>165</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>165</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2590,7 +2589,7 @@
                   <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EB0F029-E1E1-4372-919F-EF56C2E2B566}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0EB0F029-E1E1-4372-919F-EF56C2E2B566}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2642,7 +2641,7 @@
         <xdr:cNvPr id="31" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D710BBA6-6E46-43E0-B3F2-DCA86C8328EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D710BBA6-6E46-43E0-B3F2-DCA86C8328EA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2689,7 +2688,7 @@
         <xdr:cNvPr id="32" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2F013A8-C6B3-47C9-9794-BEADB267E91E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A2F013A8-C6B3-47C9-9794-BEADB267E91E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2736,7 +2735,7 @@
         <xdr:cNvPr id="33" name="Picture 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9504FAD-4F3D-414D-A9F9-0646A58DA343}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B9504FAD-4F3D-414D-A9F9-0646A58DA343}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2783,7 +2782,7 @@
         <xdr:cNvPr id="34" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D0E6B5-4ED6-4AB0-9E24-D8DB6D780715}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{27D0E6B5-4ED6-4AB0-9E24-D8DB6D780715}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2830,7 +2829,7 @@
         <xdr:cNvPr id="35" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D092F05-7DF0-48C9-9EA3-3ABF58DECA4A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0D092F05-7DF0-48C9-9EA3-3ABF58DECA4A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2877,7 +2876,7 @@
         <xdr:cNvPr id="36" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA0807F1-D09A-4D9C-85DF-A4CD38EFB3D9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{AA0807F1-D09A-4D9C-85DF-A4CD38EFB3D9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2918,13 +2917,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>161</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2934,7 +2933,7 @@
                   <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7DEA048-9E28-4EB9-A48D-A40E6DCAD4E8}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{D7DEA048-9E28-4EB9-A48D-A40E6DCAD4E8}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -2980,13 +2979,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>162</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2996,7 +2995,7 @@
                   <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CCEDD11F-B8A8-4446-A992-7F5904AFC911}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CCEDD11F-B8A8-4446-A992-7F5904AFC911}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3048,7 +3047,7 @@
         <xdr:cNvPr id="37" name="Picture 36" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED10BE3B-717C-449E-94AD-EC0543DDE145}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{ED10BE3B-717C-449E-94AD-EC0543DDE145}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3099,7 +3098,7 @@
         <xdr:cNvPr id="38" name="Picture 37" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B3907659-D7C4-40EF-90F7-C2F40CBFB8F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{B3907659-D7C4-40EF-90F7-C2F40CBFB8F1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3155,7 +3154,7 @@
         <xdr:cNvPr id="39" name="Rectangle 38">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{992469A7-6C3B-4AA7-830A-F6BC2498BC24}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{992469A7-6C3B-4AA7-830A-F6BC2498BC24}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3213,7 +3212,7 @@
         <xdr:cNvPr id="40" name="Straight Connector 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE2CCEF4-6EB5-4C39-B003-40F15B99210D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{CE2CCEF4-6EB5-4C39-B003-40F15B99210D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3265,7 +3264,7 @@
         <xdr:cNvPr id="41" name="Straight Connector 40">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19476287-F4D0-444E-BC2C-E56727DD7B32}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{19476287-F4D0-444E-BC2C-E56727DD7B32}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3312,7 +3311,7 @@
         <xdr:cNvPr id="42" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E734FED-F5C3-4A7F-A9CA-E818ECEA7391}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5E734FED-F5C3-4A7F-A9CA-E818ECEA7391}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3353,13 +3352,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>233</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>233</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3369,7 +3368,7 @@
                   <a14:compatExt spid="_x0000_s1034"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E0467C4D-3CC2-469D-AA11-5D556E4232B2}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E0467C4D-3CC2-469D-AA11-5D556E4232B2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3421,7 +3420,7 @@
         <xdr:cNvPr id="43" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CD125E8-92CC-4C0C-A00A-23B828F75EED}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5CD125E8-92CC-4C0C-A00A-23B828F75EED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3468,7 +3467,7 @@
         <xdr:cNvPr id="44" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A688B85D-EBD1-4AB9-BE47-75BA664EC0E4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A688B85D-EBD1-4AB9-BE47-75BA664EC0E4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3515,7 +3514,7 @@
         <xdr:cNvPr id="45" name="Picture 44">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C7481F9-C003-420B-8960-49DC17715A97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{5C7481F9-C003-420B-8960-49DC17715A97}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3562,7 +3561,7 @@
         <xdr:cNvPr id="46" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22CDC030-6C56-4175-88FC-31FC6A69C75C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{22CDC030-6C56-4175-88FC-31FC6A69C75C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3609,7 +3608,7 @@
         <xdr:cNvPr id="47" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{252712B1-9CF9-4B83-AF99-DAAACDC825CE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{252712B1-9CF9-4B83-AF99-DAAACDC825CE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3656,7 +3655,7 @@
         <xdr:cNvPr id="48" name="Picture 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{018E218F-C654-4465-B4F4-65499A71153E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{018E218F-C654-4465-B4F4-65499A71153E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3697,13 +3696,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>229</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>229</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3713,7 +3712,7 @@
                   <a14:compatExt spid="_x0000_s1035"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1E10ED5-2300-4C3E-8D6A-46190DCC61CA}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{A1E10ED5-2300-4C3E-8D6A-46190DCC61CA}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3759,13 +3758,13 @@
           <xdr:col>10</xdr:col>
           <xdr:colOff>38100</xdr:colOff>
           <xdr:row>230</xdr:row>
-          <xdr:rowOff>88900</xdr:rowOff>
+          <xdr:rowOff>85725</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>10</xdr:col>
-          <xdr:colOff>635000</xdr:colOff>
+          <xdr:colOff>638175</xdr:colOff>
           <xdr:row>230</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:rowOff>276225</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -3775,7 +3774,7 @@
                   <a14:compatExt spid="_x0000_s1036"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6053305B-1E3A-4018-9062-49675FF9B2C3}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6053305B-1E3A-4018-9062-49675FF9B2C3}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -3827,7 +3826,7 @@
         <xdr:cNvPr id="49" name="Picture 48" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14B16C3A-5288-4836-8705-15169CF2B872}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{14B16C3A-5288-4836-8705-15169CF2B872}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3878,7 +3877,7 @@
         <xdr:cNvPr id="50" name="Picture 49" descr="JPEG 1.jpg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD8BB44-FAC1-48B2-B3B5-BCA1D4F4FE55}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{7AD8BB44-FAC1-48B2-B3B5-BCA1D4F4FE55}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3920,9 +3919,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3960,9 +3959,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3997,7 +3996,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -4032,7 +4031,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4205,41 +4204,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71188FF3-1893-4DE7-B114-F30B2F377E8F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AL271"/>
-  <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="3.54296875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" style="3" customWidth="1"/>
-    <col min="5" max="6" width="16.54296875" style="3" customWidth="1"/>
-    <col min="7" max="8" width="11.54296875" style="3" customWidth="1"/>
-    <col min="9" max="10" width="9.54296875" style="3" customWidth="1"/>
-    <col min="11" max="12" width="11.54296875" style="3" customWidth="1"/>
-    <col min="13" max="14" width="12.54296875" style="9" customWidth="1"/>
-    <col min="15" max="16" width="9.54296875" style="9" customWidth="1"/>
-    <col min="17" max="17" width="12.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.453125" style="3"/>
-    <col min="20" max="20" width="12.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.453125" style="72" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.453125" style="72"/>
-    <col min="23" max="23" width="13.81640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="9.453125" style="72"/>
-    <col min="26" max="26" width="11.453125" style="72" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.54296875" style="72" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.1796875" style="72" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.81640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.1796875" style="72" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.453125" style="72" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.54296875" style="72" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.1796875" style="72" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="17.81640625" style="72" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.453125" style="72"/>
+    <col min="1" max="1" width="9.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="3.5703125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="3" customWidth="1"/>
+    <col min="5" max="6" width="16.5703125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="11.5703125" style="3" customWidth="1"/>
+    <col min="9" max="10" width="9.5703125" style="3" customWidth="1"/>
+    <col min="11" max="12" width="11.5703125" style="3" customWidth="1"/>
+    <col min="13" max="14" width="12.5703125" style="9" customWidth="1"/>
+    <col min="15" max="16" width="9.5703125" style="9" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.42578125" style="3"/>
+    <col min="20" max="20" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" style="72"/>
+    <col min="23" max="23" width="13.85546875" style="72" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="9.42578125" style="72"/>
+    <col min="26" max="26" width="11.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.5703125" style="72" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.85546875" style="72" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.42578125" style="72" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="72" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.140625" style="72" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="17.85546875" style="72" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.42578125" style="72"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4280,7 +4279,7 @@
       <c r="AF1" s="6"/>
       <c r="AG1" s="6"/>
     </row>
-    <row r="2" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -4317,7 +4316,7 @@
       <c r="AF2" s="6"/>
       <c r="AG2" s="6"/>
     </row>
-    <row r="3" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="9"/>
@@ -4356,7 +4355,7 @@
       <c r="AF3" s="6"/>
       <c r="AG3" s="6"/>
     </row>
-    <row r="4" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -4408,7 +4407,7 @@
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
     </row>
-    <row r="5" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -4452,7 +4451,7 @@
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
     </row>
-    <row r="6" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
@@ -4500,7 +4499,7 @@
       <c r="AF6" s="6"/>
       <c r="AG6" s="6"/>
     </row>
-    <row r="7" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -4545,7 +4544,7 @@
       <c r="AF7" s="6"/>
       <c r="AG7" s="6"/>
     </row>
-    <row r="8" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
@@ -4597,7 +4596,7 @@
       <c r="AF8" s="6"/>
       <c r="AG8" s="6"/>
     </row>
-    <row r="9" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
@@ -4608,7 +4607,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="18">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="F9" s="18"/>
       <c r="G9" s="4"/>
@@ -4650,7 +4649,7 @@
       <c r="AF9" s="6"/>
       <c r="AG9" s="6"/>
     </row>
-    <row r="10" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -4702,7 +4701,7 @@
       <c r="AF10" s="6"/>
       <c r="AG10" s="6"/>
     </row>
-    <row r="11" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -4744,7 +4743,7 @@
       <c r="AF11" s="6"/>
       <c r="AG11" s="6"/>
     </row>
-    <row r="12" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -4785,7 +4784,7 @@
       <c r="AF12" s="6"/>
       <c r="AG12" s="6"/>
     </row>
-    <row r="13" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>3</v>
       </c>
@@ -4827,7 +4826,7 @@
       <c r="AF13" s="6"/>
       <c r="AG13" s="6"/>
     </row>
-    <row r="14" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>31</v>
       </c>
@@ -4869,7 +4868,7 @@
       <c r="AF14" s="6"/>
       <c r="AG14" s="6"/>
     </row>
-    <row r="15" spans="1:33" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>32</v>
       </c>
@@ -4914,7 +4913,7 @@
       <c r="AF15" s="6"/>
       <c r="AG15" s="6"/>
     </row>
-    <row r="16" spans="1:33" s="7" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:33" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="27"/>
       <c r="B16" s="28"/>
       <c r="C16" s="10"/>
@@ -4949,7 +4948,7 @@
       <c r="AF16" s="6"/>
       <c r="AG16" s="6"/>
     </row>
-    <row r="17" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29" t="s">
         <v>33</v>
       </c>
@@ -5043,7 +5042,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>1</v>
       </c>
@@ -5153,7 +5152,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>2</v>
       </c>
@@ -5263,7 +5262,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="20" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>3</v>
       </c>
@@ -5373,7 +5372,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="21" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>4</v>
       </c>
@@ -5483,7 +5482,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="22" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>5</v>
       </c>
@@ -5597,7 +5596,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>6</v>
       </c>
@@ -5711,7 +5710,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>7</v>
       </c>
@@ -5820,7 +5819,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <v>8</v>
       </c>
@@ -5929,7 +5928,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>9</v>
       </c>
@@ -6039,7 +6038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>10</v>
       </c>
@@ -6147,7 +6146,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="36">
         <v>11</v>
       </c>
@@ -6256,7 +6255,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>12</v>
       </c>
@@ -6365,7 +6364,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36">
         <v>13</v>
       </c>
@@ -6470,7 +6469,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="13"/>
       <c r="C31" s="9"/>
@@ -6559,7 +6558,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="13"/>
       <c r="C32" s="9"/>
@@ -6648,7 +6647,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="13"/>
       <c r="C33" s="9"/>
@@ -6737,7 +6736,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="13"/>
       <c r="C34" s="9"/>
@@ -6826,7 +6825,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="13"/>
       <c r="C35" s="9"/>
@@ -6915,7 +6914,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="13"/>
       <c r="C36" s="9"/>
@@ -6955,7 +6954,7 @@
       <c r="AK36" s="56"/>
       <c r="AL36" s="56"/>
     </row>
-    <row r="37" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="13"/>
       <c r="C37" s="9"/>
@@ -6995,7 +6994,7 @@
       <c r="AK37" s="56"/>
       <c r="AL37" s="56"/>
     </row>
-    <row r="38" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="13"/>
       <c r="C38" s="9"/>
@@ -7035,7 +7034,7 @@
       <c r="AK38" s="56"/>
       <c r="AL38" s="56"/>
     </row>
-    <row r="39" spans="1:38" s="59" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:38" s="59" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="57" t="s">
         <v>61</v>
       </c>
@@ -7077,7 +7076,7 @@
       <c r="AK39" s="58"/>
       <c r="AL39" s="58"/>
     </row>
-    <row r="40" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="29" t="s">
         <v>33</v>
       </c>
@@ -7135,7 +7134,7 @@
       <c r="AK40" s="6"/>
       <c r="AL40" s="6"/>
     </row>
-    <row r="41" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="51">
         <v>1</v>
       </c>
@@ -7236,7 +7235,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="51">
         <v>2</v>
       </c>
@@ -7337,7 +7336,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51">
         <v>3</v>
       </c>
@@ -7438,7 +7437,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="51">
         <v>4</v>
       </c>
@@ -7539,7 +7538,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="51">
         <v>5</v>
       </c>
@@ -7641,7 +7640,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="46" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="51">
         <v>6</v>
       </c>
@@ -7743,7 +7742,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="47" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="51">
         <v>7</v>
       </c>
@@ -7844,7 +7843,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="51">
         <v>8</v>
       </c>
@@ -7945,7 +7944,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="51">
         <v>9</v>
       </c>
@@ -8047,7 +8046,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="51">
         <v>10</v>
       </c>
@@ -8068,7 +8067,7 @@
         <v>3970</v>
       </c>
       <c r="J50" s="39" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="K50" s="62"/>
       <c r="L50" s="64"/>
@@ -8114,7 +8113,7 @@
       </c>
       <c r="AD50" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>mm</v>
+        <v>pcs</v>
       </c>
       <c r="AE50" s="9">
         <f t="shared" si="4"/>
@@ -8148,7 +8147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="51">
         <v>11</v>
       </c>
@@ -8169,7 +8168,7 @@
         <v>7940</v>
       </c>
       <c r="J51" s="39" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="K51" s="62"/>
       <c r="L51" s="64"/>
@@ -8215,7 +8214,7 @@
       </c>
       <c r="AD51" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>mm</v>
+        <v>pcs</v>
       </c>
       <c r="AE51" s="9">
         <f t="shared" si="4"/>
@@ -8249,7 +8248,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="51">
         <v>12</v>
       </c>
@@ -8270,7 +8269,7 @@
         <v>3970</v>
       </c>
       <c r="J52" s="39" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="K52" s="62"/>
       <c r="L52" s="64"/>
@@ -8316,7 +8315,7 @@
       </c>
       <c r="AD52" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>mm</v>
+        <v>pcs</v>
       </c>
       <c r="AE52" s="9">
         <f t="shared" si="4"/>
@@ -8350,7 +8349,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="51">
         <v>13</v>
       </c>
@@ -8451,7 +8450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="51">
         <v>14</v>
       </c>
@@ -8553,7 +8552,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="51">
         <v>15</v>
       </c>
@@ -8658,7 +8657,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="51">
         <v>16</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="51">
         <v>17</v>
       </c>
@@ -8860,7 +8859,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="5"/>
       <c r="B58" s="71"/>
       <c r="C58" s="5"/>
@@ -8949,7 +8948,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
       <c r="B59" s="71"/>
       <c r="C59" s="5"/>
@@ -9038,7 +9037,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
       <c r="B60" s="71"/>
       <c r="C60" s="5"/>
@@ -9127,7 +9126,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="71"/>
       <c r="C61" s="5"/>
@@ -9216,7 +9215,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="71"/>
       <c r="C62" s="5"/>
@@ -9305,7 +9304,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="71"/>
       <c r="C63" s="5"/>
@@ -9394,7 +9393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="71"/>
       <c r="C64" s="5"/>
@@ -9483,7 +9482,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
       <c r="B65" s="71"/>
       <c r="C65" s="5"/>
@@ -9523,7 +9522,7 @@
       <c r="AK65" s="56"/>
       <c r="AL65" s="56"/>
     </row>
-    <row r="66" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
       <c r="B66" s="71"/>
       <c r="C66" s="5"/>
@@ -9563,7 +9562,7 @@
       <c r="AK66" s="56"/>
       <c r="AL66" s="56"/>
     </row>
-    <row r="67" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="9"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2" t="s">
@@ -9667,7 +9666,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>0</v>
       </c>
@@ -9708,7 +9707,7 @@
       <c r="AF69" s="6"/>
       <c r="AG69" s="6"/>
     </row>
-    <row r="70" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="2"/>
@@ -9745,7 +9744,7 @@
       <c r="AF70" s="6"/>
       <c r="AG70" s="6"/>
     </row>
-    <row r="71" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="9"/>
@@ -9784,7 +9783,7 @@
       <c r="AF71" s="6"/>
       <c r="AG71" s="6"/>
     </row>
-    <row r="72" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>5</v>
       </c>
@@ -9836,7 +9835,7 @@
       <c r="AF72" s="6"/>
       <c r="AG72" s="6"/>
     </row>
-    <row r="73" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>11</v>
       </c>
@@ -9880,7 +9879,7 @@
       <c r="AF73" s="6"/>
       <c r="AG73" s="6"/>
     </row>
-    <row r="74" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>14</v>
       </c>
@@ -9928,7 +9927,7 @@
       <c r="AF74" s="6"/>
       <c r="AG74" s="6"/>
     </row>
-    <row r="75" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>17</v>
       </c>
@@ -9973,7 +9972,7 @@
       <c r="AF75" s="6"/>
       <c r="AG75" s="6"/>
     </row>
-    <row r="76" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>22</v>
       </c>
@@ -10025,7 +10024,7 @@
       <c r="AF76" s="6"/>
       <c r="AG76" s="6"/>
     </row>
-    <row r="77" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>25</v>
       </c>
@@ -10036,7 +10035,7 @@
       <c r="D77" s="3"/>
       <c r="E77" s="18">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="F77" s="18"/>
       <c r="G77" s="4"/>
@@ -10078,7 +10077,7 @@
       <c r="AF77" s="6"/>
       <c r="AG77" s="6"/>
     </row>
-    <row r="78" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -10130,7 +10129,7 @@
       <c r="AF78" s="6"/>
       <c r="AG78" s="6"/>
     </row>
-    <row r="79" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>27</v>
       </c>
@@ -10172,7 +10171,7 @@
       <c r="AF79" s="6"/>
       <c r="AG79" s="6"/>
     </row>
-    <row r="80" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>29</v>
       </c>
@@ -10213,7 +10212,7 @@
       <c r="AF80" s="6"/>
       <c r="AG80" s="6"/>
     </row>
-    <row r="81" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>3</v>
       </c>
@@ -10255,7 +10254,7 @@
       <c r="AF81" s="6"/>
       <c r="AG81" s="6"/>
     </row>
-    <row r="82" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="25" t="s">
         <v>31</v>
       </c>
@@ -10297,7 +10296,7 @@
       <c r="AF82" s="6"/>
       <c r="AG82" s="6"/>
     </row>
-    <row r="83" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
         <v>32</v>
       </c>
@@ -10342,7 +10341,7 @@
       <c r="AF83" s="6"/>
       <c r="AG83" s="6"/>
     </row>
-    <row r="84" spans="1:38" s="7" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:38" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="27"/>
       <c r="B84" s="28"/>
       <c r="C84" s="10"/>
@@ -10377,7 +10376,7 @@
       <c r="AF84" s="6"/>
       <c r="AG84" s="6"/>
     </row>
-    <row r="85" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A85" s="29" t="s">
         <v>33</v>
       </c>
@@ -10437,7 +10436,7 @@
       <c r="AK85" s="3"/>
       <c r="AL85" s="3"/>
     </row>
-    <row r="86" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="36">
         <v>1</v>
       </c>
@@ -10547,7 +10546,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="87" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="36">
         <v>2</v>
       </c>
@@ -10657,7 +10656,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="88" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="36">
         <v>3</v>
       </c>
@@ -10767,7 +10766,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="89" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="36">
         <v>4</v>
       </c>
@@ -10877,7 +10876,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="90" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="36">
         <v>5</v>
       </c>
@@ -10986,7 +10985,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="36">
         <v>6</v>
       </c>
@@ -11095,7 +11094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="36">
         <v>7</v>
       </c>
@@ -11206,7 +11205,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="36">
         <v>8</v>
       </c>
@@ -11315,7 +11314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="36">
         <v>9</v>
       </c>
@@ -11425,7 +11424,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="36">
         <v>10</v>
       </c>
@@ -11533,7 +11532,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="36">
         <v>11</v>
       </c>
@@ -11642,7 +11641,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="36">
         <v>12</v>
       </c>
@@ -11751,7 +11750,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="36">
         <v>13</v>
       </c>
@@ -11856,7 +11855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
       <c r="B99" s="13"/>
       <c r="C99" s="9"/>
@@ -11945,7 +11944,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
       <c r="B100" s="13"/>
       <c r="C100" s="9"/>
@@ -12034,7 +12033,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
       <c r="B101" s="13"/>
       <c r="C101" s="9"/>
@@ -12123,7 +12122,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
       <c r="B102" s="13"/>
       <c r="C102" s="9"/>
@@ -12212,7 +12211,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
       <c r="B103" s="13"/>
       <c r="C103" s="9"/>
@@ -12301,7 +12300,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
       <c r="B104" s="13"/>
       <c r="C104" s="9"/>
@@ -12341,7 +12340,7 @@
       <c r="AK104" s="56"/>
       <c r="AL104" s="56"/>
     </row>
-    <row r="105" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
       <c r="B105" s="13"/>
       <c r="C105" s="9"/>
@@ -12381,7 +12380,7 @@
       <c r="AK105" s="56"/>
       <c r="AL105" s="56"/>
     </row>
-    <row r="106" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
       <c r="B106" s="13"/>
       <c r="C106" s="9"/>
@@ -12421,7 +12420,7 @@
       <c r="AK106" s="56"/>
       <c r="AL106" s="56"/>
     </row>
-    <row r="107" spans="1:38" s="59" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:38" s="59" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="57" t="s">
         <v>61</v>
       </c>
@@ -12463,7 +12462,7 @@
       <c r="AK107" s="58"/>
       <c r="AL107" s="58"/>
     </row>
-    <row r="108" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="29" t="s">
         <v>33</v>
       </c>
@@ -12521,7 +12520,7 @@
       <c r="AK108" s="6"/>
       <c r="AL108" s="6"/>
     </row>
-    <row r="109" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="51">
         <v>1</v>
       </c>
@@ -12622,7 +12621,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="51">
         <v>2</v>
       </c>
@@ -12723,7 +12722,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="51">
         <v>3</v>
       </c>
@@ -12824,7 +12823,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="51">
         <v>4</v>
       </c>
@@ -12925,7 +12924,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="51">
         <v>5</v>
       </c>
@@ -13027,7 +13026,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="114" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="51">
         <v>6</v>
       </c>
@@ -13129,7 +13128,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="115" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="51">
         <v>7</v>
       </c>
@@ -13230,7 +13229,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="51">
         <v>8</v>
       </c>
@@ -13331,7 +13330,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="51">
         <v>9</v>
       </c>
@@ -13433,7 +13432,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="118" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="51">
         <v>10</v>
       </c>
@@ -13534,7 +13533,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="51">
         <v>11</v>
       </c>
@@ -13635,7 +13634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="51">
         <v>12</v>
       </c>
@@ -13736,7 +13735,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="51">
         <v>13</v>
       </c>
@@ -13837,7 +13836,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="122" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="51">
         <v>14</v>
       </c>
@@ -13939,7 +13938,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="51">
         <v>15</v>
       </c>
@@ -14044,7 +14043,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="51">
         <v>16</v>
       </c>
@@ -14145,7 +14144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="125" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="51">
         <v>17</v>
       </c>
@@ -14246,7 +14245,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="5"/>
       <c r="B126" s="71"/>
       <c r="C126" s="5"/>
@@ -14335,7 +14334,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="5"/>
       <c r="B127" s="71"/>
       <c r="C127" s="5"/>
@@ -14424,7 +14423,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="5"/>
       <c r="B128" s="71"/>
       <c r="C128" s="5"/>
@@ -14513,7 +14512,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="129" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="5"/>
       <c r="B129" s="71"/>
       <c r="C129" s="5"/>
@@ -14602,7 +14601,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="130" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="5"/>
       <c r="B130" s="71"/>
       <c r="C130" s="5"/>
@@ -14691,7 +14690,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="5"/>
       <c r="B131" s="71"/>
       <c r="C131" s="5"/>
@@ -14780,7 +14779,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="5"/>
       <c r="B132" s="71"/>
       <c r="C132" s="5"/>
@@ -14869,7 +14868,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="133" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
       <c r="B133" s="71"/>
       <c r="C133" s="5"/>
@@ -14909,7 +14908,7 @@
       <c r="AK133" s="56"/>
       <c r="AL133" s="56"/>
     </row>
-    <row r="134" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
       <c r="B134" s="71"/>
       <c r="C134" s="5"/>
@@ -14949,7 +14948,7 @@
       <c r="AK134" s="56"/>
       <c r="AL134" s="56"/>
     </row>
-    <row r="135" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2" t="s">
@@ -15053,7 +15052,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>0</v>
       </c>
@@ -15094,7 +15093,7 @@
       <c r="AF137" s="6"/>
       <c r="AG137" s="6"/>
     </row>
-    <row r="138" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="2"/>
@@ -15131,7 +15130,7 @@
       <c r="AF138" s="6"/>
       <c r="AG138" s="6"/>
     </row>
-    <row r="139" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="9"/>
@@ -15170,7 +15169,7 @@
       <c r="AF139" s="6"/>
       <c r="AG139" s="6"/>
     </row>
-    <row r="140" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>5</v>
       </c>
@@ -15222,7 +15221,7 @@
       <c r="AF140" s="6"/>
       <c r="AG140" s="6"/>
     </row>
-    <row r="141" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>11</v>
       </c>
@@ -15266,7 +15265,7 @@
       <c r="AF141" s="6"/>
       <c r="AG141" s="6"/>
     </row>
-    <row r="142" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="15" t="s">
         <v>14</v>
       </c>
@@ -15314,7 +15313,7 @@
       <c r="AF142" s="6"/>
       <c r="AG142" s="6"/>
     </row>
-    <row r="143" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>17</v>
       </c>
@@ -15359,7 +15358,7 @@
       <c r="AF143" s="6"/>
       <c r="AG143" s="6"/>
     </row>
-    <row r="144" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>22</v>
       </c>
@@ -15411,7 +15410,7 @@
       <c r="AF144" s="6"/>
       <c r="AG144" s="6"/>
     </row>
-    <row r="145" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>25</v>
       </c>
@@ -15422,7 +15421,7 @@
       <c r="D145" s="3"/>
       <c r="E145" s="18">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="F145" s="18"/>
       <c r="G145" s="4"/>
@@ -15464,7 +15463,7 @@
       <c r="AF145" s="6"/>
       <c r="AG145" s="6"/>
     </row>
-    <row r="146" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>19</v>
       </c>
@@ -15516,7 +15515,7 @@
       <c r="AF146" s="6"/>
       <c r="AG146" s="6"/>
     </row>
-    <row r="147" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>27</v>
       </c>
@@ -15558,7 +15557,7 @@
       <c r="AF147" s="6"/>
       <c r="AG147" s="6"/>
     </row>
-    <row r="148" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>29</v>
       </c>
@@ -15599,7 +15598,7 @@
       <c r="AF148" s="6"/>
       <c r="AG148" s="6"/>
     </row>
-    <row r="149" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>3</v>
       </c>
@@ -15641,7 +15640,7 @@
       <c r="AF149" s="6"/>
       <c r="AG149" s="6"/>
     </row>
-    <row r="150" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="25" t="s">
         <v>31</v>
       </c>
@@ -15683,7 +15682,7 @@
       <c r="AF150" s="6"/>
       <c r="AG150" s="6"/>
     </row>
-    <row r="151" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="25" t="s">
         <v>32</v>
       </c>
@@ -15728,7 +15727,7 @@
       <c r="AF151" s="6"/>
       <c r="AG151" s="6"/>
     </row>
-    <row r="152" spans="1:38" s="7" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:38" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="27"/>
       <c r="B152" s="28"/>
       <c r="C152" s="10"/>
@@ -15763,7 +15762,7 @@
       <c r="AF152" s="6"/>
       <c r="AG152" s="6"/>
     </row>
-    <row r="153" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A153" s="29" t="s">
         <v>33</v>
       </c>
@@ -15823,7 +15822,7 @@
       <c r="AK153" s="3"/>
       <c r="AL153" s="3"/>
     </row>
-    <row r="154" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="36">
         <v>1</v>
       </c>
@@ -15933,7 +15932,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="155" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="36">
         <v>2</v>
       </c>
@@ -16043,7 +16042,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="156" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="36">
         <v>3</v>
       </c>
@@ -16153,7 +16152,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="157" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="36">
         <v>4</v>
       </c>
@@ -16263,7 +16262,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="158" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="36">
         <v>5</v>
       </c>
@@ -16372,7 +16371,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="159" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="36">
         <v>6</v>
       </c>
@@ -16481,7 +16480,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="160" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="36">
         <v>7</v>
       </c>
@@ -16592,7 +16591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="161" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="36">
         <v>8</v>
       </c>
@@ -16701,7 +16700,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="162" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="36">
         <v>9</v>
       </c>
@@ -16811,7 +16810,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="36">
         <v>10</v>
       </c>
@@ -16919,7 +16918,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="164" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="36">
         <v>11</v>
       </c>
@@ -17028,7 +17027,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="165" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="36">
         <v>12</v>
       </c>
@@ -17137,7 +17136,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="166" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="36">
         <v>13</v>
       </c>
@@ -17242,7 +17241,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="167" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
       <c r="B167" s="13"/>
       <c r="C167" s="9"/>
@@ -17331,7 +17330,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
       <c r="B168" s="13"/>
       <c r="C168" s="9"/>
@@ -17420,7 +17419,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="169" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
       <c r="B169" s="13"/>
       <c r="C169" s="9"/>
@@ -17509,7 +17508,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="170" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
       <c r="B170" s="13"/>
       <c r="C170" s="9"/>
@@ -17598,7 +17597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="171" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
       <c r="B171" s="13"/>
       <c r="C171" s="9"/>
@@ -17687,7 +17686,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="172" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
       <c r="B172" s="13"/>
       <c r="C172" s="9"/>
@@ -17727,7 +17726,7 @@
       <c r="AK172" s="56"/>
       <c r="AL172" s="56"/>
     </row>
-    <row r="173" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
       <c r="B173" s="13"/>
       <c r="C173" s="9"/>
@@ -17767,7 +17766,7 @@
       <c r="AK173" s="56"/>
       <c r="AL173" s="56"/>
     </row>
-    <row r="174" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
       <c r="B174" s="13"/>
       <c r="C174" s="9"/>
@@ -17807,7 +17806,7 @@
       <c r="AK174" s="56"/>
       <c r="AL174" s="56"/>
     </row>
-    <row r="175" spans="1:38" s="59" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:38" s="59" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="57" t="s">
         <v>61</v>
       </c>
@@ -17849,7 +17848,7 @@
       <c r="AK175" s="58"/>
       <c r="AL175" s="58"/>
     </row>
-    <row r="176" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="29" t="s">
         <v>33</v>
       </c>
@@ -17907,7 +17906,7 @@
       <c r="AK176" s="6"/>
       <c r="AL176" s="6"/>
     </row>
-    <row r="177" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="51">
         <v>1</v>
       </c>
@@ -18008,7 +18007,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="178" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="51">
         <v>2</v>
       </c>
@@ -18109,7 +18108,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="179" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="51">
         <v>3</v>
       </c>
@@ -18210,7 +18209,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="180" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="51">
         <v>4</v>
       </c>
@@ -18311,7 +18310,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="181" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="51">
         <v>5</v>
       </c>
@@ -18413,7 +18412,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="182" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="51">
         <v>6</v>
       </c>
@@ -18515,7 +18514,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="183" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="51">
         <v>7</v>
       </c>
@@ -18616,7 +18615,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="184" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="51">
         <v>8</v>
       </c>
@@ -18717,7 +18716,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="185" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="51">
         <v>9</v>
       </c>
@@ -18819,7 +18818,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="186" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="51">
         <v>10</v>
       </c>
@@ -18920,7 +18919,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="187" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="51">
         <v>11</v>
       </c>
@@ -19021,7 +19020,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="188" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="51">
         <v>12</v>
       </c>
@@ -19122,7 +19121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="189" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="51">
         <v>13</v>
       </c>
@@ -19223,7 +19222,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="190" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="51">
         <v>14</v>
       </c>
@@ -19325,7 +19324,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="51">
         <v>15</v>
       </c>
@@ -19430,7 +19429,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="192" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="51">
         <v>16</v>
       </c>
@@ -19531,7 +19530,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="193" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="51">
         <v>17</v>
       </c>
@@ -19632,7 +19631,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="194" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="71"/>
       <c r="C194" s="5"/>
@@ -19721,7 +19720,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="195" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="71"/>
       <c r="C195" s="5"/>
@@ -19810,7 +19809,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="196" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="71"/>
       <c r="C196" s="5"/>
@@ -19899,7 +19898,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="197" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="71"/>
       <c r="C197" s="5"/>
@@ -19988,7 +19987,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="198" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="71"/>
       <c r="C198" s="5"/>
@@ -20077,7 +20076,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="199" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="71"/>
       <c r="C199" s="5"/>
@@ -20166,7 +20165,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="200" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="71"/>
       <c r="C200" s="5"/>
@@ -20255,7 +20254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="201" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
       <c r="B201" s="71"/>
       <c r="C201" s="5"/>
@@ -20295,7 +20294,7 @@
       <c r="AK201" s="56"/>
       <c r="AL201" s="56"/>
     </row>
-    <row r="202" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
       <c r="B202" s="71"/>
       <c r="C202" s="5"/>
@@ -20335,7 +20334,7 @@
       <c r="AK202" s="56"/>
       <c r="AL202" s="56"/>
     </row>
-    <row r="203" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="9"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2" t="s">
@@ -20439,7 +20438,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="205" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>0</v>
       </c>
@@ -20480,7 +20479,7 @@
       <c r="AF205" s="6"/>
       <c r="AG205" s="6"/>
     </row>
-    <row r="206" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="2"/>
@@ -20517,7 +20516,7 @@
       <c r="AF206" s="6"/>
       <c r="AG206" s="6"/>
     </row>
-    <row r="207" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="9"/>
@@ -20556,7 +20555,7 @@
       <c r="AF207" s="6"/>
       <c r="AG207" s="6"/>
     </row>
-    <row r="208" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>5</v>
       </c>
@@ -20608,7 +20607,7 @@
       <c r="AF208" s="6"/>
       <c r="AG208" s="6"/>
     </row>
-    <row r="209" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>11</v>
       </c>
@@ -20652,7 +20651,7 @@
       <c r="AF209" s="6"/>
       <c r="AG209" s="6"/>
     </row>
-    <row r="210" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" s="15" t="s">
         <v>14</v>
       </c>
@@ -20700,7 +20699,7 @@
       <c r="AF210" s="6"/>
       <c r="AG210" s="6"/>
     </row>
-    <row r="211" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>17</v>
       </c>
@@ -20745,7 +20744,7 @@
       <c r="AF211" s="6"/>
       <c r="AG211" s="6"/>
     </row>
-    <row r="212" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>22</v>
       </c>
@@ -20797,7 +20796,7 @@
       <c r="AF212" s="6"/>
       <c r="AG212" s="6"/>
     </row>
-    <row r="213" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>25</v>
       </c>
@@ -20808,7 +20807,7 @@
       <c r="D213" s="3"/>
       <c r="E213" s="18">
         <f ca="1">TODAY()</f>
-        <v>46205</v>
+        <v>46220</v>
       </c>
       <c r="F213" s="18"/>
       <c r="G213" s="4"/>
@@ -20850,7 +20849,7 @@
       <c r="AF213" s="6"/>
       <c r="AG213" s="6"/>
     </row>
-    <row r="214" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>19</v>
       </c>
@@ -20902,7 +20901,7 @@
       <c r="AF214" s="6"/>
       <c r="AG214" s="6"/>
     </row>
-    <row r="215" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>27</v>
       </c>
@@ -20944,7 +20943,7 @@
       <c r="AF215" s="6"/>
       <c r="AG215" s="6"/>
     </row>
-    <row r="216" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>29</v>
       </c>
@@ -20985,7 +20984,7 @@
       <c r="AF216" s="6"/>
       <c r="AG216" s="6"/>
     </row>
-    <row r="217" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>3</v>
       </c>
@@ -21027,7 +21026,7 @@
       <c r="AF217" s="6"/>
       <c r="AG217" s="6"/>
     </row>
-    <row r="218" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" s="25" t="s">
         <v>31</v>
       </c>
@@ -21069,7 +21068,7 @@
       <c r="AF218" s="6"/>
       <c r="AG218" s="6"/>
     </row>
-    <row r="219" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:38" s="7" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" s="25" t="s">
         <v>32</v>
       </c>
@@ -21114,7 +21113,7 @@
       <c r="AF219" s="6"/>
       <c r="AG219" s="6"/>
     </row>
-    <row r="220" spans="1:38" s="7" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:38" s="7" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="27"/>
       <c r="B220" s="28"/>
       <c r="C220" s="10"/>
@@ -21149,7 +21148,7 @@
       <c r="AF220" s="6"/>
       <c r="AG220" s="6"/>
     </row>
-    <row r="221" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A221" s="29" t="s">
         <v>33</v>
       </c>
@@ -21209,7 +21208,7 @@
       <c r="AK221" s="3"/>
       <c r="AL221" s="3"/>
     </row>
-    <row r="222" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="36">
         <v>1</v>
       </c>
@@ -21319,7 +21318,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="223" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="36">
         <v>2</v>
       </c>
@@ -21429,7 +21428,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="224" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="36">
         <v>3</v>
       </c>
@@ -21539,7 +21538,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="225" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="36">
         <v>4</v>
       </c>
@@ -21649,7 +21648,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="226" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="36">
         <v>5</v>
       </c>
@@ -21758,7 +21757,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="227" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="36">
         <v>6</v>
       </c>
@@ -21867,7 +21866,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="228" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="36">
         <v>7</v>
       </c>
@@ -21978,7 +21977,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="229" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="36">
         <v>8</v>
       </c>
@@ -22087,7 +22086,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="230" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="36">
         <v>9</v>
       </c>
@@ -22197,7 +22196,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="231" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="36">
         <v>10</v>
       </c>
@@ -22305,7 +22304,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="232" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="36">
         <v>11</v>
       </c>
@@ -22414,7 +22413,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="233" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="36">
         <v>12</v>
       </c>
@@ -22523,7 +22522,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="234" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:38" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="36">
         <v>13</v>
       </c>
@@ -22628,7 +22627,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="235" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5"/>
       <c r="B235" s="13"/>
       <c r="C235" s="9"/>
@@ -22717,7 +22716,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="236" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5"/>
       <c r="B236" s="13"/>
       <c r="C236" s="9"/>
@@ -22806,7 +22805,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="237" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5"/>
       <c r="B237" s="13"/>
       <c r="C237" s="9"/>
@@ -22895,7 +22894,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="238" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5"/>
       <c r="B238" s="13"/>
       <c r="C238" s="9"/>
@@ -22984,7 +22983,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="239" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5"/>
       <c r="B239" s="13"/>
       <c r="C239" s="9"/>
@@ -23073,7 +23072,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="240" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5"/>
       <c r="B240" s="13"/>
       <c r="C240" s="9"/>
@@ -23113,7 +23112,7 @@
       <c r="AK240" s="56"/>
       <c r="AL240" s="56"/>
     </row>
-    <row r="241" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5"/>
       <c r="B241" s="13"/>
       <c r="C241" s="9"/>
@@ -23153,7 +23152,7 @@
       <c r="AK241" s="56"/>
       <c r="AL241" s="56"/>
     </row>
-    <row r="242" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:38" s="44" customFormat="1" ht="29.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5"/>
       <c r="B242" s="13"/>
       <c r="C242" s="9"/>
@@ -23193,7 +23192,7 @@
       <c r="AK242" s="56"/>
       <c r="AL242" s="56"/>
     </row>
-    <row r="243" spans="1:38" s="59" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:38" s="59" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="57" t="s">
         <v>61</v>
       </c>
@@ -23235,7 +23234,7 @@
       <c r="AK243" s="58"/>
       <c r="AL243" s="58"/>
     </row>
-    <row r="244" spans="1:38" s="7" customFormat="1" ht="29.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:38" s="7" customFormat="1" ht="29.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="29" t="s">
         <v>33</v>
       </c>
@@ -23293,7 +23292,7 @@
       <c r="AK244" s="6"/>
       <c r="AL244" s="6"/>
     </row>
-    <row r="245" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="51">
         <v>1</v>
       </c>
@@ -23394,7 +23393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="246" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="51">
         <v>2</v>
       </c>
@@ -23495,7 +23494,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="247" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="51">
         <v>3</v>
       </c>
@@ -23596,7 +23595,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="248" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="51">
         <v>4</v>
       </c>
@@ -23697,7 +23696,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="249" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="51">
         <v>5</v>
       </c>
@@ -23799,7 +23798,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="250" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="51">
         <v>6</v>
       </c>
@@ -23901,7 +23900,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="251" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="51">
         <v>7</v>
       </c>
@@ -24002,7 +24001,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="252" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="51">
         <v>8</v>
       </c>
@@ -24103,7 +24102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="253" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="51">
         <v>9</v>
       </c>
@@ -24205,7 +24204,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="254" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="51">
         <v>10</v>
       </c>
@@ -24306,7 +24305,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="255" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="51">
         <v>11</v>
       </c>
@@ -24407,7 +24406,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="256" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="51">
         <v>12</v>
       </c>
@@ -24508,7 +24507,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="257" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="51">
         <v>13</v>
       </c>
@@ -24609,7 +24608,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="258" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="51">
         <v>14</v>
       </c>
@@ -24711,7 +24710,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="259" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="51">
         <v>15</v>
       </c>
@@ -24816,7 +24815,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="260" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="51">
         <v>16</v>
       </c>
@@ -24917,7 +24916,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="261" spans="1:38" s="44" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:38" s="44" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="51">
         <v>17</v>
       </c>
@@ -25018,7 +25017,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="262" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="71"/>
       <c r="C262" s="5"/>
@@ -25107,7 +25106,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="263" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="71"/>
       <c r="C263" s="5"/>
@@ -25196,7 +25195,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="264" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="71"/>
       <c r="C264" s="5"/>
@@ -25285,7 +25284,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="265" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="71"/>
       <c r="C265" s="5"/>
@@ -25374,7 +25373,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="266" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="71"/>
       <c r="C266" s="5"/>
@@ -25463,7 +25462,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="267" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="71"/>
       <c r="C267" s="5"/>
@@ -25552,7 +25551,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="268" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="71"/>
       <c r="C268" s="5"/>
@@ -25641,7 +25640,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="269" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5"/>
       <c r="B269" s="71"/>
       <c r="C269" s="5"/>
@@ -25681,7 +25680,7 @@
       <c r="AK269" s="56"/>
       <c r="AL269" s="56"/>
     </row>
-    <row r="270" spans="1:38" s="44" customFormat="1" ht="15.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:38" s="44" customFormat="1" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5"/>
       <c r="B270" s="71"/>
       <c r="C270" s="5"/>
@@ -25721,7 +25720,7 @@
       <c r="AK270" s="56"/>
       <c r="AL270" s="56"/>
     </row>
-    <row r="271" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:38" s="59" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="9"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2" t="s">
@@ -25850,13 +25849,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>29</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>29</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -25875,13 +25874,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>25</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>25</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -25900,13 +25899,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -25925,13 +25924,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>97</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>97</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -25950,13 +25949,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>93</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>93</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -25975,13 +25974,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>94</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>94</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26000,13 +25999,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>165</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>165</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26025,13 +26024,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>161</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>161</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26050,13 +26049,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>162</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>162</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26075,13 +26074,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>233</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>233</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26100,13 +26099,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>229</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>229</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -26125,13 +26124,13 @@
                 <xdr:col>10</xdr:col>
                 <xdr:colOff>38100</xdr:colOff>
                 <xdr:row>230</xdr:row>
-                <xdr:rowOff>88900</xdr:rowOff>
+                <xdr:rowOff>85725</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>10</xdr:col>
-                <xdr:colOff>635000</xdr:colOff>
+                <xdr:colOff>638175</xdr:colOff>
                 <xdr:row>230</xdr:row>
-                <xdr:rowOff>279400</xdr:rowOff>
+                <xdr:rowOff>276225</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
